--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M27B1_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M27B1_IN_Piura.xlsx
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.01</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>3.04</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>38.2</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C13" s="29">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>50.06</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>8.69</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1907,11 +1907,11 @@
       </c>
       <c r="B15" s="42">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>448.8038</v>
       </c>
       <c r="C15" s="43">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="41" t="inlineStr">
         <is>
@@ -1932,11 +1932,11 @@
       </c>
       <c r="B16" s="45">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>13.6982</v>
       </c>
       <c r="C16" s="46">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>3.05</v>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
@@ -1957,11 +1957,11 @@
       </c>
       <c r="B17" s="45">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>435.1056</v>
       </c>
       <c r="C17" s="46">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>96.95</v>
       </c>
       <c r="D17" s="44" t="inlineStr">
         <is>
@@ -2136,11 +2136,11 @@
       </c>
       <c r="B28" s="22">
         <f>SUM(B25:B27)</f>
-        <v/>
+        <v>449.0662</v>
       </c>
       <c r="C28" s="23">
         <f>SUM(C25:C27)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D28" s="17" t="inlineStr"/>
       <c r="E28" s="17" t="inlineStr"/>
@@ -2259,6 +2259,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2508,6 +2509,7 @@
       <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="17" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -2552,6 +2554,7 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="168" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -2738,11 +2741,11 @@
       </c>
       <c r="B11" s="31">
         <f>SUM(B10:B10)</f>
-        <v/>
+        <v>448.8</v>
       </c>
       <c r="C11" s="23">
         <f>SUM(C10:C10)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -2752,19 +2755,19 @@
       <c r="E11" s="17" t="inlineStr"/>
       <c r="F11" s="17">
         <f>ROUND(AVERAGE(F10:F10),2)</f>
-        <v/>
+        <v>17.86</v>
       </c>
       <c r="G11" s="22">
         <f>ROUND(AVERAGE(G10:G10),4)</f>
-        <v/>
+        <v>0.3632</v>
       </c>
       <c r="H11" s="23">
         <f>ROUND(AVERAGE(H10:H10),2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I11" s="23">
         <f>ROUND(AVERAGE(I10:I10),2)</f>
-        <v/>
+        <v>96.95</v>
       </c>
     </row>
     <row r="12"/>
